--- a/artfynd/A 40531-2024 artfynd.xlsx
+++ b/artfynd/A 40531-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,592 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120108570</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91863</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stenkullen, Stenkullen, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>580499</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6508785</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120108571</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91863</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stenkullen, Stenkullen, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>580328</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6508882</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120108579</v>
+      </c>
+      <c r="B5" t="n">
+        <v>94681</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stenkullen, Stenkullen, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>580409</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6508853</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120108578</v>
+      </c>
+      <c r="B6" t="n">
+        <v>94681</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stenkullen, Stenkullen, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>580426</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6508694</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120108577</v>
+      </c>
+      <c r="B7" t="n">
+        <v>94681</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stenkullen, Stenkullen, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>580206</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6508698</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40531-2024 artfynd.xlsx
+++ b/artfynd/A 40531-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119933439</v>
+        <v>120108579</v>
       </c>
       <c r="B2" t="n">
-        <v>91863</v>
+        <v>94681</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580252</v>
+        <v>580409</v>
       </c>
       <c r="R2" t="n">
-        <v>6509279</v>
+        <v>6508853</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -748,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120108570</v>
+        <v>120108577</v>
       </c>
       <c r="B3" t="n">
-        <v>91863</v>
+        <v>94681</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,34 +803,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580499</v>
+        <v>580206</v>
       </c>
       <c r="R3" t="n">
-        <v>6508785</v>
+        <v>6508698</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -872,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1028,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120108579</v>
+        <v>120108570</v>
       </c>
       <c r="B5" t="n">
-        <v>94681</v>
+        <v>91863</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,31 +1038,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1072,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580409</v>
+        <v>580499</v>
       </c>
       <c r="R5" t="n">
-        <v>6508853</v>
+        <v>6508785</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1107,7 +1108,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1117,7 +1118,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1260,43 +1261,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120108577</v>
+        <v>119933439</v>
       </c>
       <c r="B7" t="n">
-        <v>94681</v>
+        <v>91863</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580206</v>
+        <v>580252</v>
       </c>
       <c r="R7" t="n">
-        <v>6508698</v>
+        <v>6509279</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1334,22 +1334,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 40531-2024 artfynd.xlsx
+++ b/artfynd/A 40531-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120108579</v>
+        <v>120108577</v>
       </c>
       <c r="B2" t="n">
         <v>94681</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580409</v>
+        <v>580206</v>
       </c>
       <c r="R2" t="n">
-        <v>6508853</v>
+        <v>6508698</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120108577</v>
+        <v>120108578</v>
       </c>
       <c r="B3" t="n">
         <v>94681</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580206</v>
+        <v>580426</v>
       </c>
       <c r="R3" t="n">
-        <v>6508698</v>
+        <v>6508694</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120108571</v>
+        <v>120108579</v>
       </c>
       <c r="B4" t="n">
-        <v>91863</v>
+        <v>94681</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,34 +919,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580328</v>
+        <v>580409</v>
       </c>
       <c r="R4" t="n">
-        <v>6508882</v>
+        <v>6508853</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1145,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120108578</v>
+        <v>120108571</v>
       </c>
       <c r="B6" t="n">
-        <v>94681</v>
+        <v>91863</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,31 +1154,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580426</v>
+        <v>580328</v>
       </c>
       <c r="R6" t="n">
-        <v>6508694</v>
+        <v>6508882</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 40531-2024 artfynd.xlsx
+++ b/artfynd/A 40531-2024 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120108578</v>
+        <v>120108571</v>
       </c>
       <c r="B3" t="n">
-        <v>94681</v>
+        <v>91863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,31 +803,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580426</v>
+        <v>580328</v>
       </c>
       <c r="R3" t="n">
-        <v>6508694</v>
+        <v>6508882</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1142,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120108571</v>
+        <v>120108578</v>
       </c>
       <c r="B6" t="n">
-        <v>91863</v>
+        <v>94681</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,34 +1157,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580328</v>
+        <v>580426</v>
       </c>
       <c r="R6" t="n">
-        <v>6508882</v>
+        <v>6508694</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 40531-2024 artfynd.xlsx
+++ b/artfynd/A 40531-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120108577</v>
+        <v>120108570</v>
       </c>
       <c r="B2" t="n">
-        <v>94681</v>
+        <v>91881</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580206</v>
+        <v>580499</v>
       </c>
       <c r="R2" t="n">
-        <v>6508698</v>
+        <v>6508785</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120108571</v>
+        <v>120108578</v>
       </c>
       <c r="B3" t="n">
-        <v>91863</v>
+        <v>94704</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +806,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580328</v>
+        <v>580426</v>
       </c>
       <c r="R3" t="n">
-        <v>6508882</v>
+        <v>6508694</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120108579</v>
+        <v>120108576</v>
       </c>
       <c r="B4" t="n">
-        <v>94681</v>
+        <v>94704</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580409</v>
+        <v>580206</v>
       </c>
       <c r="R4" t="n">
-        <v>6508853</v>
+        <v>6508698</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120108570</v>
+        <v>120108571</v>
       </c>
       <c r="B5" t="n">
-        <v>91863</v>
+        <v>91881</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1073,13 +1073,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580499</v>
+        <v>580328</v>
       </c>
       <c r="R5" t="n">
-        <v>6508785</v>
+        <v>6508882</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120108578</v>
+        <v>120108579</v>
       </c>
       <c r="B6" t="n">
-        <v>94681</v>
+        <v>94704</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580426</v>
+        <v>580409</v>
       </c>
       <c r="R6" t="n">
-        <v>6508694</v>
+        <v>6508853</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,7 +1264,7 @@
         <v>119933439</v>
       </c>
       <c r="B7" t="n">
-        <v>91863</v>
+        <v>91881</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 40531-2024 artfynd.xlsx
+++ b/artfynd/A 40531-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120108570</v>
+        <v>120108577</v>
       </c>
       <c r="B2" t="n">
-        <v>91881</v>
+        <v>94704</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580499</v>
+        <v>580206</v>
       </c>
       <c r="R2" t="n">
-        <v>6508785</v>
+        <v>6508698</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -757,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120108578</v>
+        <v>120108570</v>
       </c>
       <c r="B3" t="n">
-        <v>94704</v>
+        <v>91881</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,31 +803,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580426</v>
+        <v>580499</v>
       </c>
       <c r="R3" t="n">
-        <v>6508694</v>
+        <v>6508785</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,7 +910,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120108576</v>
+        <v>120108579</v>
       </c>
       <c r="B4" t="n">
         <v>94704</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580206</v>
+        <v>580409</v>
       </c>
       <c r="R4" t="n">
-        <v>6508698</v>
+        <v>6508853</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120108571</v>
+        <v>120108578</v>
       </c>
       <c r="B5" t="n">
-        <v>91881</v>
+        <v>94704</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,34 +1038,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1073,13 +1070,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580328</v>
+        <v>580426</v>
       </c>
       <c r="R5" t="n">
-        <v>6508882</v>
+        <v>6508694</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1118,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120108579</v>
+        <v>120108571</v>
       </c>
       <c r="B6" t="n">
-        <v>94704</v>
+        <v>91881</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,31 +1154,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580409</v>
+        <v>580328</v>
       </c>
       <c r="R6" t="n">
-        <v>6508853</v>
+        <v>6508882</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 40531-2024 artfynd.xlsx
+++ b/artfynd/A 40531-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120108577</v>
+        <v>120108570</v>
       </c>
       <c r="B2" t="n">
-        <v>94704</v>
+        <v>91881</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580206</v>
+        <v>580499</v>
       </c>
       <c r="R2" t="n">
-        <v>6508698</v>
+        <v>6508785</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120108570</v>
+        <v>120108578</v>
       </c>
       <c r="B3" t="n">
-        <v>91881</v>
+        <v>94704</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +806,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580499</v>
+        <v>580426</v>
       </c>
       <c r="R3" t="n">
-        <v>6508785</v>
+        <v>6508694</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,7 +910,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120108579</v>
+        <v>120108577</v>
       </c>
       <c r="B4" t="n">
         <v>94704</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580409</v>
+        <v>580206</v>
       </c>
       <c r="R4" t="n">
-        <v>6508853</v>
+        <v>6508698</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120108578</v>
+        <v>120108579</v>
       </c>
       <c r="B5" t="n">
         <v>94704</v>
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580426</v>
+        <v>580409</v>
       </c>
       <c r="R5" t="n">
-        <v>6508694</v>
+        <v>6508853</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 40531-2024 artfynd.xlsx
+++ b/artfynd/A 40531-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120108570</v>
+        <v>120108577</v>
       </c>
       <c r="B2" t="n">
-        <v>91881</v>
+        <v>94704</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580499</v>
+        <v>580206</v>
       </c>
       <c r="R2" t="n">
-        <v>6508785</v>
+        <v>6508698</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -757,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120108578</v>
+        <v>120108571</v>
       </c>
       <c r="B3" t="n">
-        <v>94704</v>
+        <v>91881</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,31 +803,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580426</v>
+        <v>580328</v>
       </c>
       <c r="R3" t="n">
-        <v>6508694</v>
+        <v>6508882</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,7 +910,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120108577</v>
+        <v>120108578</v>
       </c>
       <c r="B4" t="n">
         <v>94704</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580206</v>
+        <v>580426</v>
       </c>
       <c r="R4" t="n">
-        <v>6508698</v>
+        <v>6508694</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1142,7 +1142,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120108571</v>
+        <v>120108570</v>
       </c>
       <c r="B6" t="n">
         <v>91881</v>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580328</v>
+        <v>580499</v>
       </c>
       <c r="R6" t="n">
-        <v>6508882</v>
+        <v>6508785</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1374,6 +1374,1230 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120477442</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stenkullen, Stenkullen, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>580236</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6508906</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Frida Blixt</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Frida Blixt</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120477624</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stenkullen, Stenkullen, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>580277</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6508990</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120479222</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Svartgölen, Svartgölen, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>580501</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6508961</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120476985</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stenkullen, Stenkullen, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>580228</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6508867</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Frida Blixt</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Frida Blixt</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120476656</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>580155</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6508764</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120476959</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stenkullen, Stenkullen, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>580189</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6508870</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120479578</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Svartgölen, Svartgölen, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>580486</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6508929</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Frida Blixt</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Frida Blixt</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120479010</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Svartgölen, Svartgölen, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>580458</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6509011</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Frida Blixt</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Frida Blixt</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120480654</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Svartgölen, Svartgölen, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>580495</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6508896</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Frida Blixt</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Frida Blixt</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120477601</v>
+      </c>
+      <c r="B17" t="n">
+        <v>8432</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stenkullen, Stenkullen, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>580254</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6508909</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Frida Blixt</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Frida Blixt</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120477708</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stenkullen, Stenkullen, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>580248</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6509035</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120482405</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Svartgölen, Svartgölen, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>580446</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6508834</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Frida Blixt</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Frida Blixt</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40531-2024 artfynd.xlsx
+++ b/artfynd/A 40531-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120108577</v>
+        <v>120108579</v>
       </c>
       <c r="B2" t="n">
         <v>94704</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580206</v>
+        <v>580409</v>
       </c>
       <c r="R2" t="n">
-        <v>6508698</v>
+        <v>6508853</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -910,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120108578</v>
+        <v>120108570</v>
       </c>
       <c r="B4" t="n">
-        <v>94704</v>
+        <v>91881</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,31 +922,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580426</v>
+        <v>580499</v>
       </c>
       <c r="R4" t="n">
-        <v>6508694</v>
+        <v>6508785</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -989,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1029,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120108579</v>
+        <v>120108577</v>
       </c>
       <c r="B5" t="n">
         <v>94704</v>
@@ -1070,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580409</v>
+        <v>580206</v>
       </c>
       <c r="R5" t="n">
-        <v>6508853</v>
+        <v>6508698</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1105,7 +1108,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1118,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120108570</v>
+        <v>120108578</v>
       </c>
       <c r="B6" t="n">
-        <v>91881</v>
+        <v>94704</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,34 +1157,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580499</v>
+        <v>580426</v>
       </c>
       <c r="R6" t="n">
-        <v>6508785</v>
+        <v>6508694</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1376,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120477442</v>
+        <v>120477624</v>
       </c>
       <c r="B8" t="n">
-        <v>91881</v>
+        <v>79160</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,21 +1392,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1416,13 +1416,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580236</v>
+        <v>580277</v>
       </c>
       <c r="R8" t="n">
-        <v>6508906</v>
+        <v>6508990</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1466,22 +1466,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120477624</v>
+        <v>120480654</v>
       </c>
       <c r="B9" t="n">
-        <v>79160</v>
+        <v>91881</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,37 +1494,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stenkullen, Stenkullen, Srm</t>
+          <t>Svartgölen, Svartgölen, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580277</v>
+        <v>580495</v>
       </c>
       <c r="R9" t="n">
-        <v>6508990</v>
+        <v>6508896</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,22 +1568,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120479222</v>
+        <v>120477637</v>
       </c>
       <c r="B10" t="n">
-        <v>79160</v>
+        <v>91881</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,37 +1596,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svartgölen, Svartgölen, Srm</t>
+          <t>Stenkullen, Stenkullen, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580501</v>
+        <v>580236</v>
       </c>
       <c r="R10" t="n">
-        <v>6508961</v>
+        <v>6508906</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1670,22 +1670,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120476985</v>
+        <v>120479222</v>
       </c>
       <c r="B11" t="n">
-        <v>91881</v>
+        <v>79160</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1698,37 +1698,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stenkullen, Stenkullen, Srm</t>
+          <t>Svartgölen, Svartgölen, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580228</v>
+        <v>580501</v>
       </c>
       <c r="R11" t="n">
-        <v>6508867</v>
+        <v>6508961</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1772,22 +1772,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120476656</v>
+        <v>120479578</v>
       </c>
       <c r="B12" t="n">
-        <v>91881</v>
+        <v>79160</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1800,37 +1800,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Srm</t>
+          <t>Svartgölen, Svartgölen, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580155</v>
+        <v>580486</v>
       </c>
       <c r="R12" t="n">
-        <v>6508764</v>
+        <v>6508929</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1874,22 +1874,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120476959</v>
+        <v>120477708</v>
       </c>
       <c r="B13" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1898,25 +1898,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580189</v>
+        <v>580248</v>
       </c>
       <c r="R13" t="n">
-        <v>6508870</v>
+        <v>6509035</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1988,10 +1988,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120479578</v>
+        <v>120476656</v>
       </c>
       <c r="B14" t="n">
-        <v>79160</v>
+        <v>91881</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2004,37 +2004,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartgölen, Svartgölen, Srm</t>
+          <t>Jungfruberget, Jungfruberget, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580486</v>
+        <v>580155</v>
       </c>
       <c r="R14" t="n">
-        <v>6508929</v>
+        <v>6508764</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2078,12 +2078,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120480654</v>
+        <v>120476959</v>
       </c>
       <c r="B16" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2204,41 +2204,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartgölen, Svartgölen, Srm</t>
+          <t>Stenkullen, Stenkullen, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580495</v>
+        <v>580189</v>
       </c>
       <c r="R16" t="n">
-        <v>6508896</v>
+        <v>6508870</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2282,22 +2282,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120477601</v>
+        <v>120476985</v>
       </c>
       <c r="B17" t="n">
-        <v>8432</v>
+        <v>91881</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2306,25 +2306,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580254</v>
+        <v>580228</v>
       </c>
       <c r="R17" t="n">
-        <v>6508909</v>
+        <v>6508867</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2396,10 +2396,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120477708</v>
+        <v>120477601</v>
       </c>
       <c r="B18" t="n">
-        <v>79160</v>
+        <v>8432</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2408,25 +2408,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2436,13 +2436,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580248</v>
+        <v>580254</v>
       </c>
       <c r="R18" t="n">
-        <v>6509035</v>
+        <v>6508909</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2486,12 +2486,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 40531-2024 artfynd.xlsx
+++ b/artfynd/A 40531-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120108579</v>
+        <v>120108577</v>
       </c>
       <c r="B2" t="n">
         <v>94704</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580409</v>
+        <v>580206</v>
       </c>
       <c r="R2" t="n">
-        <v>6508853</v>
+        <v>6508698</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120108571</v>
+        <v>120108570</v>
       </c>
       <c r="B3" t="n">
         <v>91881</v>
@@ -826,7 +826,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580328</v>
+        <v>580499</v>
       </c>
       <c r="R3" t="n">
-        <v>6508882</v>
+        <v>6508785</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120108570</v>
+        <v>120108578</v>
       </c>
       <c r="B4" t="n">
-        <v>91881</v>
+        <v>94704</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,34 +922,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580499</v>
+        <v>580426</v>
       </c>
       <c r="R4" t="n">
-        <v>6508785</v>
+        <v>6508694</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -992,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120108577</v>
+        <v>120108571</v>
       </c>
       <c r="B5" t="n">
-        <v>94704</v>
+        <v>91881</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,31 +1038,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1073,13 +1073,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580206</v>
+        <v>580328</v>
       </c>
       <c r="R5" t="n">
-        <v>6508698</v>
+        <v>6508882</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,7 +1145,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120108578</v>
+        <v>120108579</v>
       </c>
       <c r="B6" t="n">
         <v>94704</v>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580426</v>
+        <v>580409</v>
       </c>
       <c r="R6" t="n">
-        <v>6508694</v>
+        <v>6508853</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1376,7 +1376,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120477624</v>
+        <v>120479578</v>
       </c>
       <c r="B8" t="n">
         <v>79160</v>
@@ -1412,17 +1412,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stenkullen, Stenkullen, Srm</t>
+          <t>Svartgölen, Svartgölen, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580277</v>
+        <v>580486</v>
       </c>
       <c r="R8" t="n">
-        <v>6508990</v>
+        <v>6508929</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1466,19 +1466,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120480654</v>
+        <v>120479010</v>
       </c>
       <c r="B9" t="n">
         <v>91881</v>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580495</v>
+        <v>580458</v>
       </c>
       <c r="R9" t="n">
-        <v>6508896</v>
+        <v>6509011</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,7 +1580,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120477637</v>
+        <v>120482405</v>
       </c>
       <c r="B10" t="n">
         <v>91881</v>
@@ -1616,14 +1616,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stenkullen, Stenkullen, Srm</t>
+          <t>Svartgölen, Svartgölen, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580236</v>
+        <v>580446</v>
       </c>
       <c r="R10" t="n">
-        <v>6508906</v>
+        <v>6508834</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120479222</v>
+        <v>120477708</v>
       </c>
       <c r="B11" t="n">
         <v>79160</v>
@@ -1718,14 +1718,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svartgölen, Svartgölen, Srm</t>
+          <t>Stenkullen, Stenkullen, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580501</v>
+        <v>580248</v>
       </c>
       <c r="R11" t="n">
-        <v>6508961</v>
+        <v>6509035</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1784,7 +1784,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120479578</v>
+        <v>120477624</v>
       </c>
       <c r="B12" t="n">
         <v>79160</v>
@@ -1820,17 +1820,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svartgölen, Svartgölen, Srm</t>
+          <t>Stenkullen, Stenkullen, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580486</v>
+        <v>580277</v>
       </c>
       <c r="R12" t="n">
-        <v>6508929</v>
+        <v>6508990</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1874,22 +1874,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120477708</v>
+        <v>120476959</v>
       </c>
       <c r="B13" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1898,25 +1898,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580248</v>
+        <v>580189</v>
       </c>
       <c r="R13" t="n">
-        <v>6509035</v>
+        <v>6508870</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1988,7 +1988,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120476656</v>
+        <v>120476985</v>
       </c>
       <c r="B14" t="n">
         <v>91881</v>
@@ -2024,17 +2024,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Srm</t>
+          <t>Stenkullen, Stenkullen, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580155</v>
+        <v>580228</v>
       </c>
       <c r="R14" t="n">
-        <v>6508764</v>
+        <v>6508867</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2078,22 +2078,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120479010</v>
+        <v>120479222</v>
       </c>
       <c r="B15" t="n">
-        <v>91881</v>
+        <v>79160</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2106,21 +2106,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2130,13 +2130,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580458</v>
+        <v>580501</v>
       </c>
       <c r="R15" t="n">
-        <v>6509011</v>
+        <v>6508961</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2180,22 +2180,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120476959</v>
+        <v>120476656</v>
       </c>
       <c r="B16" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2204,41 +2204,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stenkullen, Stenkullen, Srm</t>
+          <t>Jungfruberget, Jungfruberget, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580189</v>
+        <v>580155</v>
       </c>
       <c r="R16" t="n">
-        <v>6508870</v>
+        <v>6508764</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120476985</v>
+        <v>120480654</v>
       </c>
       <c r="B17" t="n">
         <v>91881</v>
@@ -2330,14 +2330,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stenkullen, Stenkullen, Srm</t>
+          <t>Svartgölen, Svartgölen, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580228</v>
+        <v>580495</v>
       </c>
       <c r="R17" t="n">
-        <v>6508867</v>
+        <v>6508896</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2396,10 +2396,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120477601</v>
+        <v>120477442</v>
       </c>
       <c r="B18" t="n">
-        <v>8432</v>
+        <v>91881</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2408,25 +2408,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580254</v>
+        <v>580236</v>
       </c>
       <c r="R18" t="n">
-        <v>6508909</v>
+        <v>6508906</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2498,10 +2498,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120482405</v>
+        <v>120477601</v>
       </c>
       <c r="B19" t="n">
-        <v>91881</v>
+        <v>8432</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2510,38 +2510,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svartgölen, Svartgölen, Srm</t>
+          <t>Stenkullen, Stenkullen, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580446</v>
+        <v>580254</v>
       </c>
       <c r="R19" t="n">
-        <v>6508834</v>
+        <v>6508909</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 40531-2024 artfynd.xlsx
+++ b/artfynd/A 40531-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120108577</v>
+        <v>120108578</v>
       </c>
       <c r="B2" t="n">
         <v>94704</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580206</v>
+        <v>580426</v>
       </c>
       <c r="R2" t="n">
-        <v>6508698</v>
+        <v>6508694</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120108570</v>
+        <v>120108577</v>
       </c>
       <c r="B3" t="n">
-        <v>91881</v>
+        <v>94704</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580499</v>
+        <v>580206</v>
       </c>
       <c r="R3" t="n">
-        <v>6508785</v>
+        <v>6508698</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -873,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120108578</v>
+        <v>120108571</v>
       </c>
       <c r="B4" t="n">
-        <v>94704</v>
+        <v>91881</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,31 +919,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580426</v>
+        <v>580328</v>
       </c>
       <c r="R4" t="n">
-        <v>6508694</v>
+        <v>6508882</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120108571</v>
+        <v>120108579</v>
       </c>
       <c r="B5" t="n">
-        <v>91881</v>
+        <v>94704</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,34 +1038,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1073,13 +1070,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580328</v>
+        <v>580409</v>
       </c>
       <c r="R5" t="n">
-        <v>6508882</v>
+        <v>6508853</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1118,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120108579</v>
+        <v>120108570</v>
       </c>
       <c r="B6" t="n">
-        <v>94704</v>
+        <v>91881</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,31 +1154,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580409</v>
+        <v>580499</v>
       </c>
       <c r="R6" t="n">
-        <v>6508853</v>
+        <v>6508785</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1376,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120479578</v>
+        <v>120476959</v>
       </c>
       <c r="B8" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,41 +1388,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svartgölen, Svartgölen, Srm</t>
+          <t>Stenkullen, Stenkullen, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580486</v>
+        <v>580189</v>
       </c>
       <c r="R8" t="n">
-        <v>6508929</v>
+        <v>6508870</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1466,22 +1466,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120479010</v>
+        <v>120477708</v>
       </c>
       <c r="B9" t="n">
-        <v>91881</v>
+        <v>79160</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,37 +1494,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartgölen, Svartgölen, Srm</t>
+          <t>Stenkullen, Stenkullen, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580458</v>
+        <v>580248</v>
       </c>
       <c r="R9" t="n">
-        <v>6509011</v>
+        <v>6509035</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,19 +1568,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120482405</v>
+        <v>120476656</v>
       </c>
       <c r="B10" t="n">
         <v>91881</v>
@@ -1616,17 +1616,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svartgölen, Svartgölen, Srm</t>
+          <t>Jungfruberget, Jungfruberget, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580446</v>
+        <v>580155</v>
       </c>
       <c r="R10" t="n">
-        <v>6508834</v>
+        <v>6508764</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1670,22 +1670,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120477708</v>
+        <v>120480654</v>
       </c>
       <c r="B11" t="n">
-        <v>79160</v>
+        <v>91881</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1698,37 +1698,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stenkullen, Stenkullen, Srm</t>
+          <t>Svartgölen, Svartgölen, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580248</v>
+        <v>580495</v>
       </c>
       <c r="R11" t="n">
-        <v>6509035</v>
+        <v>6508896</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1772,19 +1772,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120477624</v>
+        <v>120479222</v>
       </c>
       <c r="B12" t="n">
         <v>79160</v>
@@ -1820,14 +1820,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stenkullen, Stenkullen, Srm</t>
+          <t>Svartgölen, Svartgölen, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580277</v>
+        <v>580501</v>
       </c>
       <c r="R12" t="n">
-        <v>6508990</v>
+        <v>6508961</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1886,10 +1886,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120476959</v>
+        <v>120479010</v>
       </c>
       <c r="B13" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1898,41 +1898,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stenkullen, Stenkullen, Srm</t>
+          <t>Svartgölen, Svartgölen, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580189</v>
+        <v>580458</v>
       </c>
       <c r="R13" t="n">
-        <v>6508870</v>
+        <v>6509011</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1976,22 +1976,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120476985</v>
+        <v>120479578</v>
       </c>
       <c r="B14" t="n">
-        <v>91881</v>
+        <v>79160</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2004,34 +2004,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stenkullen, Stenkullen, Srm</t>
+          <t>Svartgölen, Svartgölen, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580228</v>
+        <v>580486</v>
       </c>
       <c r="R14" t="n">
-        <v>6508867</v>
+        <v>6508929</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2090,10 +2090,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120479222</v>
+        <v>120477601</v>
       </c>
       <c r="B15" t="n">
-        <v>79160</v>
+        <v>8432</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2102,41 +2102,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartgölen, Svartgölen, Srm</t>
+          <t>Stenkullen, Stenkullen, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580501</v>
+        <v>580254</v>
       </c>
       <c r="R15" t="n">
-        <v>6508961</v>
+        <v>6508909</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2180,22 +2180,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120476656</v>
+        <v>120477624</v>
       </c>
       <c r="B16" t="n">
-        <v>91881</v>
+        <v>79160</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2208,37 +2208,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Srm</t>
+          <t>Stenkullen, Stenkullen, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580155</v>
+        <v>580277</v>
       </c>
       <c r="R16" t="n">
-        <v>6508764</v>
+        <v>6508990</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120480654</v>
+        <v>120477442</v>
       </c>
       <c r="B17" t="n">
         <v>91881</v>
@@ -2330,14 +2330,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svartgölen, Svartgölen, Srm</t>
+          <t>Stenkullen, Stenkullen, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580495</v>
+        <v>580236</v>
       </c>
       <c r="R17" t="n">
-        <v>6508896</v>
+        <v>6508906</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2396,7 +2396,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120477442</v>
+        <v>120476985</v>
       </c>
       <c r="B18" t="n">
         <v>91881</v>
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580236</v>
+        <v>580228</v>
       </c>
       <c r="R18" t="n">
-        <v>6508906</v>
+        <v>6508867</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2498,10 +2498,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120477601</v>
+        <v>120482405</v>
       </c>
       <c r="B19" t="n">
-        <v>8432</v>
+        <v>91881</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2510,38 +2510,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stenkullen, Stenkullen, Srm</t>
+          <t>Svartgölen, Svartgölen, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580254</v>
+        <v>580446</v>
       </c>
       <c r="R19" t="n">
-        <v>6508909</v>
+        <v>6508834</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 40531-2024 artfynd.xlsx
+++ b/artfynd/A 40531-2024 artfynd.xlsx
@@ -2954,7 +2954,7 @@
         <v>120979317</v>
       </c>
       <c r="B23" t="n">
-        <v>57501</v>
+        <v>57504</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>120975024</v>
       </c>
       <c r="B24" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 40531-2024 artfynd.xlsx
+++ b/artfynd/A 40531-2024 artfynd.xlsx
@@ -2719,7 +2719,7 @@
         <v>120700110</v>
       </c>
       <c r="B21" t="n">
-        <v>56576</v>
+        <v>56581</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 40531-2024 artfynd.xlsx
+++ b/artfynd/A 40531-2024 artfynd.xlsx
@@ -2734,11 +2734,6 @@
       <c r="E21" t="n">
         <v>102612</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Järpe</t>
-        </is>
-      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>Tetrastes bonasia</t>

--- a/artfynd/A 40531-2024 artfynd.xlsx
+++ b/artfynd/A 40531-2024 artfynd.xlsx
@@ -2719,7 +2719,7 @@
         <v>120700110</v>
       </c>
       <c r="B21" t="n">
-        <v>56581</v>
+        <v>56585</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2733,6 +2733,11 @@
       </c>
       <c r="E21" t="n">
         <v>102612</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
